--- a/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Domain_by_Sample_Type.xlsx
+++ b/R_Codes/DataSummary/All_Prokaryotes/Sample_Type/All_Prokaryotes_Summary_Domain_by_Sample_Type.xlsx
@@ -387,10 +387,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>74.3463355796281</v>
+        <v>74.3480115595076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.141171938920425</v>
+        <v>0.141310157320179</v>
       </c>
     </row>
     <row r="3">
@@ -401,10 +401,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>25.6536644203717</v>
+        <v>25.6519884404912</v>
       </c>
       <c r="D3" t="n">
-        <v>0.159810419054134</v>
+        <v>0.159781326491811</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>77.640078578483</v>
+        <v>77.3553129488753</v>
       </c>
       <c r="D2" t="n">
-        <v>0.208398705269819</v>
+        <v>0.209499706920512</v>
       </c>
     </row>
     <row r="3">
@@ -454,10 +454,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>22.3599214215169</v>
+        <v>22.6446870511251</v>
       </c>
       <c r="D3" t="n">
-        <v>0.355911524633001</v>
+        <v>0.361804727754346</v>
       </c>
     </row>
   </sheetData>
